--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +77,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,11 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12812,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12866,6 +12884,117 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>CLUB_S2004_05_0108</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2004_05_0091 'HC Kroměříž' prev→CLUB_S2003_04_0194 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2004_05_0222 'HC Frýdek Místek' prev→CLUB_S2003_04_0087 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2004_05_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2004_05_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2004_05_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0021</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0021 'Baráž o Extraligu' (L15, parent=NODE_S2004_05_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0028</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0028 'Baráž o I.ligu' (L15, parent=NODE_S2004_05_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0042</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0042 'O postup do I.ligy' (L25, parent=NODE_S2004_05_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -16158,8 +16287,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16239,7 +16366,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -30472,6 +30598,237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0091</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0091 'HC Kroměříž' prev→CLUB_S2003_04_0194 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0222</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0222 'HC Frýdek Místek' prev→CLUB_S2003_04_0087 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0029</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0030</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0031</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0021</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2004_05_0021 'Baráž o Extraligu' (L15, parent=NODE_S2004_05_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0028</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2004_05_0028 'Baráž o I.ligu' (L15, parent=NODE_S2004_05_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0042</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2004_05_0042 'O postup do I.ligy' (L25, parent=NODE_S2004_05_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12830,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12890,7 +12890,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2004_05_0091 'HC Kroměříž' prev→CLUB_S2003_04_0194 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12902,7 +12902,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2004_05_0222 'HC Frýdek Místek' prev→CLUB_S2003_04_0087 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -12914,7 +12914,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2004_05_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2004_05_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12938,7 +12938,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2004_05_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12948,14 +12948,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2004_05_0021</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0021 'Baráž o Extraligu' (L15, parent=NODE_S2004_05_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -12965,14 +12960,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S2004_05_0028</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0028 'Baráž o I.ligu' (L15, parent=NODE_S2004_05_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12982,17 +12972,336 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S2004_05_0042</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2004_05_0042 'O postup do I.ligy' (L25, parent=NODE_S2004_05_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Český Krumlov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0044 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0194 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0179 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Světlá nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0181 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lázně Bělohrad' → 'Police nad Metují' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0087 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16287,6 +16596,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16317,6 +16628,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0001</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16329,6 +16645,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0003</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16341,6 +16662,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0003</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16353,6 +16679,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0036</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16366,6 +16697,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -22240,12 +22572,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -22334,12 +22666,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22418,12 +22750,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22460,12 +22792,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -22544,12 +22876,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22843,12 +23175,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -22927,12 +23259,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -23085,12 +23417,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Český Krumlov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Český Krumlov</t>
         </is>
       </c>
     </row>
@@ -23954,12 +24286,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -24117,12 +24449,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -24952,12 +25284,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -25681,12 +26013,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov.</t>
+          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov. || TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>VHS HC Benešov</t>
+          <t>Benešov</t>
         </is>
       </c>
     </row>
@@ -26447,12 +26779,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -26615,12 +26947,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26867,12 +27199,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -27077,12 +27409,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -27203,12 +27535,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -27712,12 +28044,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28505,12 +28837,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -28668,12 +29000,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -28752,12 +29084,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Světlá nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -28925,12 +29257,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -29318,12 +29650,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Spartak Lázně Bělohrad. city ✓. || Lázně Bělohrad = Spartak Lázně Bělohrad (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Lázně Bělohrad.</t>
+          <t>Spartak Lázně Bělohrad. city ✓. || Lázně Bělohrad = Spartak Lázně Bělohrad (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Lázně Bělohrad. || TBD: city 'Lázně Bělohrad' → 'Police nad Metují' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Lázně Bělohrad</t>
+          <t>Police nad Metují</t>
         </is>
       </c>
     </row>
@@ -29434,12 +29766,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -30007,12 +30339,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno.</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
@@ -30604,11 +30936,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -30653,21 +30985,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0091</t>
+          <t>CLUB_S2004_05_0013</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0091 'HC Kroměříž' prev→CLUB_S2003_04_0194 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -30675,21 +31005,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0222</t>
+          <t>CLUB_S2004_05_0015</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0222 'HC Frýdek Místek' prev→CLUB_S2003_04_0087 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -30697,21 +31025,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0029</t>
+          <t>CLUB_S2004_05_0017</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -30719,21 +31045,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0030</t>
+          <t>CLUB_S2004_05_0018</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -30741,21 +31065,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0031</t>
+          <t>CLUB_S2004_05_0020</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -30763,21 +31085,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2004_05_0021</t>
+          <t>CLUB_S2004_05_0027</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2004_05_0021 'Baráž o Extraligu' (L15, parent=NODE_S2004_05_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -30785,21 +31105,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S2004_05_0028</t>
+          <t>CLUB_S2004_05_0029</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2004_05_0028 'Baráž o I.ligu' (L15, parent=NODE_S2004_05_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -30807,24 +31125,562 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S2004_05_0042</t>
+          <t>CLUB_S2004_05_0035</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2004_05_0042 'O postup do I.ligy' (L25, parent=NODE_S2004_05_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Český Krumlov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0054</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0044 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0062</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0066</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0071</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0089</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0091</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0194 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0106</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0125</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0125</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0129</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0136</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0141</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0144</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0157</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0165</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0168</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0179 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0174</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0178</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0182</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0184</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Světlá nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0188</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0191</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0181 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0198</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lázně Bělohrad' → 'Police nad Metují' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0203</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0215</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0217</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0222</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0087 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -13208,7 +13208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13272,6 +13272,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16728,8 +16738,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16859,7 +16867,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -13460,6 +13460,16 @@
           <t>NODE_S2004_05_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13474,6 +13484,14 @@
         <is>
           <t>NODE_S2003_04_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -13648,6 +13666,16 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13662,6 +13690,14 @@
         <is>
           <t>NODE_S2003_04_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13742,6 +13778,16 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13756,6 +13802,14 @@
         <is>
           <t>NODE_S2003_04_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -13789,6 +13843,16 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13803,6 +13867,14 @@
         <is>
           <t>NODE_S2003_04_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -13836,6 +13908,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13850,6 +13924,14 @@
         <is>
           <t>NODE_S2003_04_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -13883,6 +13965,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13897,6 +13981,14 @@
         <is>
           <t>NODE_S2003_04_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -13930,6 +14022,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13944,6 +14038,14 @@
         <is>
           <t>NODE_S2003_04_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -13977,6 +14079,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13991,6 +14095,14 @@
         <is>
           <t>NODE_S2003_04_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -14024,6 +14136,8 @@
           <t>NODE_S2004_05_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14038,6 +14152,14 @@
         <is>
           <t>NODE_S2003_04_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -14071,6 +14193,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14085,6 +14209,14 @@
         <is>
           <t>NODE_S2003_04_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -14118,6 +14250,8 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14132,6 +14266,14 @@
         <is>
           <t>NODE_S2003_04_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -14165,6 +14307,16 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14179,6 +14331,14 @@
         <is>
           <t>NODE_S2003_04_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -14306,6 +14466,16 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14320,6 +14490,14 @@
         <is>
           <t>NODE_S2003_04_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14353,6 +14531,16 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14367,6 +14555,14 @@
         <is>
           <t>NODE_S2003_04_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -14400,6 +14596,12 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14414,6 +14616,14 @@
         <is>
           <t>NODE_S2003_04_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -14447,6 +14657,12 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14461,6 +14677,14 @@
         <is>
           <t>NODE_S2003_04_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -14494,6 +14718,8 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14508,6 +14734,14 @@
         <is>
           <t>NODE_S2003_04_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -14541,6 +14775,8 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14555,6 +14791,14 @@
         <is>
           <t>NODE_S2003_04_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14818,6 +15062,12 @@
           <t>NODE_S2004_05_0032</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0034</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14832,6 +15082,14 @@
         <is>
           <t>NODE_S2003_04_0033</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -14865,6 +15123,8 @@
           <t>NODE_S2004_05_0032</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14874,6 +15134,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -14907,6 +15175,8 @@
           <t>NODE_S2004_05_0032</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14916,6 +15186,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -15090,6 +15368,12 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15104,6 +15388,14 @@
         <is>
           <t>NODE_S2003_04_0038</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -15137,6 +15429,12 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15151,6 +15449,14 @@
         <is>
           <t>NODE_S2003_04_0039</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -15184,6 +15490,8 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15198,6 +15506,14 @@
         <is>
           <t>NODE_S2003_04_0040</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -15325,6 +15641,8 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15339,6 +15657,14 @@
         <is>
           <t>NODE_S2003_04_0043</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -15466,6 +15792,12 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15480,6 +15812,14 @@
         <is>
           <t>NODE_S2003_04_0046</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -15775,6 +16115,12 @@
           <t>NODE_S2004_05_0053</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0055</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15789,6 +16135,14 @@
         <is>
           <t>NODE_S2003_04_0049</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -15822,6 +16176,8 @@
           <t>NODE_S2004_05_0053</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15836,6 +16192,14 @@
         <is>
           <t>NODE_S2003_04_0050</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -15916,6 +16280,12 @@
           <t>NODE_S2004_05_0056</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0058</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15930,6 +16300,14 @@
         <is>
           <t>NODE_S2003_04_0052</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>4 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -15963,6 +16341,8 @@
           <t>NODE_S2004_05_0056</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15977,6 +16357,14 @@
         <is>
           <t>NODE_S2003_04_0053</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -16188,6 +16576,12 @@
           <t>REG_VYC</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0064</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16207,6 +16601,14 @@
         <is>
           <t>NODE_S2003_04_0059</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>28 týmů</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -16240,6 +16642,8 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16254,6 +16658,14 @@
         <is>
           <t>NODE_S2003_04_0060</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -16287,6 +16699,8 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16296,6 +16710,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -16329,6 +16751,8 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16343,6 +16767,14 @@
         <is>
           <t>NODE_S2003_04_0060</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -16423,6 +16855,12 @@
           <t>NODE_S2004_05_0067</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0069</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16432,6 +16870,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -16465,6 +16911,8 @@
           <t>NODE_S2004_05_0067</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16474,6 +16922,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -16554,6 +17010,12 @@
           <t>NODE_S2004_05_0070</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0074</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16563,6 +17025,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -16680,6 +17150,8 @@
           <t>NODE_S2004_05_0070</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16694,6 +17166,14 @@
         <is>
           <t>NODE_S2003_04_0070</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -16738,6 +17218,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -16867,6 +17349,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -907,6 +907,11 @@
           <t>HC Moeller Pardubice (C)</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>52</v>
       </c>
@@ -13908,8 +13913,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13965,8 +13968,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14022,8 +14023,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14079,8 +14078,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14136,8 +14133,6 @@
           <t>NODE_S2004_05_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14193,8 +14188,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14250,8 +14243,6 @@
           <t>NODE_S2004_05_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14601,7 +14592,6 @@
           <t>NODE_S2004_05_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14662,7 +14652,6 @@
           <t>NODE_S2004_05_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14718,8 +14707,6 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14775,8 +14762,6 @@
           <t>NODE_S2004_05_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15067,7 +15052,6 @@
           <t>NODE_S2004_05_0034</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15123,8 +15107,6 @@
           <t>NODE_S2004_05_0032</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15175,8 +15157,6 @@
           <t>NODE_S2004_05_0032</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15373,7 +15353,6 @@
           <t>NODE_S2004_05_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15434,7 +15413,6 @@
           <t>NODE_S2004_05_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15490,8 +15468,6 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15641,8 +15617,6 @@
           <t>NODE_S2004_05_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15797,7 +15771,6 @@
           <t>NODE_S2004_05_0039</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16120,7 +16093,6 @@
           <t>NODE_S2004_05_0055</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16176,8 +16148,6 @@
           <t>NODE_S2004_05_0053</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16285,7 +16255,6 @@
           <t>NODE_S2004_05_0058</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16341,8 +16310,6 @@
           <t>NODE_S2004_05_0056</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16581,7 +16548,6 @@
           <t>NODE_S2004_05_0064</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16642,8 +16608,6 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16699,8 +16663,6 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16751,8 +16713,6 @@
           <t>NODE_S2004_05_0063</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16860,7 +16820,6 @@
           <t>NODE_S2004_05_0069</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16911,8 +16870,6 @@
           <t>NODE_S2004_05_0067</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17015,7 +16972,6 @@
           <t>NODE_S2004_05_0074</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17150,8 +17106,6 @@
           <t>NODE_S2004_05_0070</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17218,8 +17172,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -17349,7 +17301,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -31135,7 +31086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31315,6 +31266,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Moeller Pardubice</t>
         </is>
       </c>
     </row>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -17172,6 +17172,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -17301,6 +17303,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -4490,7 +4490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8556,6 +8556,618 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0270</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00338</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0271</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0272</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00340</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0273</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00341</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0274</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00342</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0275</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00343</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0276</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00344</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0277</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00345</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0278</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00346</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0279</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00347</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0280</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00348</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0281</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00349</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0282</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00350</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8567,7 +9179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9805,6 +10417,658 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0283</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00351</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SK Reinpo</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0284</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00352</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0285</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00353</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0286</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00354</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0287</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00355</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Granit</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0288</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00356</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0289</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00357</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0290</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00358</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0291</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00359</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0292</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00360</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0293</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00361</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0294</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00362</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0295</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00363</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Reinpo</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0296</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00364</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9816,7 +11080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12019,6 +13283,73 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0081</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0081</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0297</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00365</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12030,7 +13361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12824,6 +14155,298 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0298</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00366</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0299</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00367</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0300</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00368</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0301</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00369</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0302</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00370</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0303</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00371</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13213,7 +14836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17329,6 +18952,255 @@
       <c r="A90" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Středočeský – Kladno</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0048</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Jihočeský – Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0053</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0079</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Východočeský – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0063</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0080</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vysočina – Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0067</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0081</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>REG_JHM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0070</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0082</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Severomoravský – Opava</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0075</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -22583,7 +24455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -31075,6 +32947,2475 @@
       <c r="J202" t="inlineStr">
         <is>
           <t>Jelínek Vítkovice-Svinov</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0227</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SK Černošice</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SK Černošice</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0228</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0229</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0230</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0231</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0232</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0233</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0234</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0235</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>HC 1988 Kladno B</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>HC 1988 Kladno B</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0236</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0237</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0238</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0239</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0240</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0241</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0242</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0243</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0244</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0245</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0246</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0247</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0248</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0249</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0250</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0251</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0252</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0253</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0254</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0255</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0256</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0257</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0258</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0259</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0260</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0261</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0262</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0263</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0264</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0265</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0266</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0267</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0268</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0269</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0270</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0271</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0272</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0273</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0274</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0275</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0276</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0277</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0278</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0279</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0280</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0281</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0282</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0283</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0284</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SK Reinpo</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SK Reinpo</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0285</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0286</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0287</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0288</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HC Granit</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HC Granit</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0289</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0290</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0291</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0292</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0293</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0294</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0295</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0296</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HC Reinpo</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HC Reinpo</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0297</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0298</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0299</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0300</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0301</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0302</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0303</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -37875,7 +42216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39728,6 +44069,118 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SK Černošice</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0227</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0228</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00296</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39739,7 +44192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -43101,6 +47554,874 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0229</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0230</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0231</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0232</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0233</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0234</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HC 1988 Kladno B</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0235</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0236</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0237</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0238</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0239</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0240</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0241</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0242</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0243</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0244</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0245</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00313</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0246</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Kladno</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0077</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0247</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00315</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43112,7 +48433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -44487,6 +49808,1018 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>SER_S2004_05_0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0248</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0249</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0250</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nová Bystřice</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0251</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0252</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0253</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kunžak</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0254</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0255</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0256</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0257</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0258</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0259</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00327</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0260</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00328</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0261</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00329</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0262</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00330</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0263</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00331</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0264</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00332</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0265</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00333</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0266</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00334</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HC Slavoj Český Krumlov dor.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0267</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00335</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0268</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00336</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0078</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0269</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2004_05_00337</t>
         </is>
       </c>
     </row>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +86,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +115,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18795,8 +18806,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -18926,7 +18935,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -35636,7 +35644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35693,7 +35701,7 @@
           <t>CLUB_S2004_05_0013</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35713,7 +35721,7 @@
           <t>CLUB_S2004_05_0020</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35733,7 +35741,7 @@
           <t>CLUB_S2004_05_0029</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35753,7 +35761,7 @@
           <t>CLUB_S2004_05_0054</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0044 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -35773,7 +35781,7 @@
           <t>CLUB_S2004_05_0062</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35793,7 +35801,7 @@
           <t>CLUB_S2004_05_0066</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -35813,7 +35821,7 @@
           <t>CLUB_S2004_05_0071</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -35833,7 +35841,7 @@
           <t>CLUB_S2004_05_0089</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35853,7 +35861,7 @@
           <t>CLUB_S2004_05_0091</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0194 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -35873,7 +35881,7 @@
           <t>CLUB_S2004_05_0106</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35893,7 +35901,7 @@
           <t>CLUB_S2004_05_0125</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35913,7 +35921,7 @@
           <t>CLUB_S2004_05_0157</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -35933,7 +35941,7 @@
           <t>CLUB_S2004_05_0165</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -35953,7 +35961,7 @@
           <t>CLUB_S2004_05_0168</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0179 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -35973,7 +35981,7 @@
           <t>CLUB_S2004_05_0174</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -35993,7 +36001,7 @@
           <t>CLUB_S2004_05_0178</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36013,7 +36021,7 @@
           <t>CLUB_S2004_05_0182</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36033,7 +36041,7 @@
           <t>CLUB_S2004_05_0191</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0181 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -36053,7 +36061,7 @@
           <t>CLUB_S2004_05_0215</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -36073,7 +36081,7 @@
           <t>CLUB_S2004_05_0217</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -36093,11 +36101,89 @@
           <t>CLUB_S2004_05_0222</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2003_04_0087 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>30_Východočeský L40 finále (východní Čechy) · NODE_S2004_05_0066</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Sokol Doubravice ,Spartak Police nad Metují a Lázně Bělohrad zpět z), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor · NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (SK Černošice, Benátky nad Jizerou B), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Jihomoravský – Žďár nad Sázavou (Jihomoravský kraj) · NODE_S2004_05_0081</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Jiskra Vír), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F22"/>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14469,7 +14472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14773,6 +14776,57 @@
         </is>
       </c>
       <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0066</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Sokol Doubravice ,Spartak Police nad Metují a Lázně Bělohrad zpět z), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0076</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (SK Černošice, Benátky nad Jizerou B), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Jiskra Vír), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -36121,7 +36175,7 @@
           <t>30_Východočeský L40 finále (východní Čechy) · NODE_S2004_05_0066</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (Sokol Doubravice ,Spartak Police nad Metují a Lázně Bělohrad zpět z), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -36147,7 +36201,7 @@
           <t>Praha – Pražský přebor · NODE_S2004_05_0076</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (SK Černošice, Benátky nad Jizerou B), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -36173,7 +36227,7 @@
           <t>Jihomoravský – Žďár nad Sázavou (Jihomoravský kraj) · NODE_S2004_05_0081</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Jiskra Vír), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -16581,7 +16581,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40 finále</t>
+          <t>Praha, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o 5. -10.místo</t>
+          <t>Praha, 4. úroveň, skupina o 5. -10.místo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A</t>
+          <t>Středočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B</t>
+          <t>Středočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina o  9.-14.místo</t>
+          <t>Středočeský, 4. úroveň, skupina o 9.-14.místo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finále</t>
+          <t>Jihočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Ústecký L40 základní část</t>
+          <t>Ústecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Ústecký L40 finále</t>
+          <t>Ústecký, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40 základní část</t>
+          <t>Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina o 9.-16.místo</t>
+          <t>Východočeský, 4. úroveň, skupina o 9.-16.místo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 základní část</t>
+          <t>Vysočina, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 finále</t>
+          <t>Vysočina, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18860,6 +18860,8 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -18892,7 +18894,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -18989,6 +18991,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>

--- a/data/S2004_05_FINAL.xlsx
+++ b/data/S2004_05_FINAL.xlsx
@@ -4759,7 +4759,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -18860,8 +18860,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -18991,7 +18989,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
@@ -22715,7 +22712,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -22793,7 +22790,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -22871,7 +22868,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -22949,7 +22946,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -23027,7 +23024,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -23105,7 +23102,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -23183,7 +23180,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -23266,7 +23263,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -23344,7 +23341,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -23422,7 +23419,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -23500,7 +23497,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -23578,7 +23575,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -23656,7 +23653,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -23734,7 +23731,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -37165,7 +37162,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -37243,7 +37240,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -37321,7 +37318,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -37394,7 +37391,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -37509,7 +37506,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -37587,7 +37584,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -37665,7 +37662,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -37738,7 +37735,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -38821,7 +38818,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -38899,7 +38896,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -38972,7 +38969,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -39050,7 +39047,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -40712,7 +40709,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -40790,7 +40787,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -40868,7 +40865,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -40946,7 +40943,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -42647,7 +42644,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -42725,7 +42722,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -42803,7 +42800,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -42881,7 +42878,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
